--- a/stories/arbres/TREE-VIV-001.xlsx
+++ b/stories/arbres/TREE-VIV-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Noé est à l'école, avec maman. Dans la cour, un chien arrive. Le chien aboie. Ouaf ouaf. Maman dit : le nom de l'animal, c'est chien. Le cri, c'est ouaf. Un chat saute. Miaou. Noé dit : chat. Miaou. On nomme l'animal. On dit le cri. On dit le nom de l'animal. On dit le cri.</t>
+          <t>Aujourd'hui, Noé est à l'école, avec maman. Dans la cour, un chien arrive. Le chien aboie. Ouaf ouaf. Le nom de l'animal, c'est chien. Le cri, c'est ouaf. Un chat saute. Miaou. Chat. Miaou. On nomme l'animal. On dit le cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,14 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Noé est à l'école, avec maman. Dans la cour, un chien arrive. Le chien aboie. Ouaf ouaf.
+maman|Le nom de l'animal, c'est chien.
+narrateur|Le cri, c'est ouaf. Un chat saute. Miaou.
+enfant-m|Chat. Miaou. On nomme l'animal. On dit le cri. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1512,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1541,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers la cuisine de l'école. Ça sent la soupe. Sur l'affiche, une vache. Maman dit : vache. Le cri, c'est meuh. Noé répète : vache. Meuh. Le nom de l'animal, et le cri. On dit le nom de l'animal. On dit le cri.</t>
+          <t>Noé va vers la cuisine de l'école. Ça sent la soupe. Sur l'affiche, une vache. Vache. Le cri, c'est meuh. Noé répète : vache. Meuh. Le nom de l'animal, et le cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1679,13 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers la cuisine de l'école. Ça sent la soupe. Sur l'affiche, une vache.
+maman|Vache.
+narrateur|Le cri, c'est meuh. Noé répète : vache. Meuh. Le nom de l'animal, et le cri. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien fait ouaf. Quel est son cri ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Noé a dit le nom de l'animal. Noé a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2230,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2207,7 +2259,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Noé prend le ballon rouge. Un pigeon roucoule. Sur le ballon, un mouton. Maman dit : mouton. Béé. Noé dit le nom de l'animal. Noé dit le cri. On dit le nom de l'animal. On dit le cri.</t>
+          <t>Noé prend le ballon rouge. Un pigeon roucoule. Sur le ballon, un mouton. Mouton. Béé. Noé dit le nom de l'animal. Noé dit le cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2345,6 +2397,13 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le ballon rouge. Un pigeon roucoule. Sur le ballon, un mouton.
+maman|Mouton. Béé.
+narrateur|Noé dit le nom de l'animal. Noé dit le cri. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2592,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2761,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. La lumière est claire. On parle tout bas. On a dit le nom de l'animal. On a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2928,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3095,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Des miettes dorment sur la table. On range les jouets. On a dit le nom de l'animal. On a dit le cri. Chat, miaou. On dit le nom de l'animal. On dit le cri. Maman serre Noé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3262,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3429,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On s'assoit un moment. On a dit le nom de l'animal. On a dit le cri. Vache, meuh. On dit le nom de l'animal. On dit le cri. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3596,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3763,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le seau bleu. Un pain croustille. Dans le seau, un dessin de coq. Cocorico. Noé nomme l'animal. Noé dit le cri. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3859,6 +3958,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3883,7 +3987,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. Les chaussures font toc toc. On respire, un, deux. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range. Maman dit : c'est bien.</t>
+          <t>Noé rejoint Tom. Les chaussures font toc toc. On respire, un, deux. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4021,6 +4125,12 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Les chaussures font toc toc. On respire, un, deux. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4293,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4460,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. La couverture est douce. On referme le sac. On a dit le nom de l'animal. On a dit le cri. Canard, coin coin. On dit le nom de l'animal. On dit le cri. On souffle. Noé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4627,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4794,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Une cloche tinte au loin. On essuie une miette. On a dit le nom de l'animal. On a dit le cri. Mouton, béé. On dit le nom de l'animal. On dit le cri. Noé prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4961,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5128,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le doudou. Un pain croustille. Noé serre le doudou. Le doudou a des oreilles de chat. Miaou. Nom de l'animal, cri. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5321,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5490,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Le bois sent le chaud. On met le doudou près. On a dit le nom de l'animal. On a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5657,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5824,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Une goutte tombe, ploc. On lace les chaussures. On a dit le nom de l'animal. On a dit le cri. Chat, miaou. On dit le nom de l'animal. On dit le cri. Maman serre Noé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5991,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6158,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Le savon sent la fleur. On met le manteau. On a dit le nom de l'animal. On a dit le cri. Vache, meuh. On dit le nom de l'animal. On dit le cri. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6325,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6354,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers le jardin. L'herbe chatouille. Un coq est dessiné sur le mur. Maman dit : coq. Cocorico. Noé dit le nom de l'animal. Noé dit le cri. Cocorico. On dit le nom de l'animal. On dit le cri.</t>
+          <t>Noé va vers le jardin. L'herbe chatouille. Un coq est dessiné sur le mur. Coq. Cocorico. Noé dit le nom de l'animal. Noé dit le cri. Cocorico. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6492,13 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le jardin. L'herbe chatouille. Un coq est dessiné sur le mur.
+maman|Coq. Cocorico.
+narrateur|Noé dit le nom de l'animal. Noé dit le cri. Cocorico. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6679,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Miaou. C'est le cri de qui ?</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6852,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Chat, miaou. Maman sourit. Nom de l'animal, cri. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7043,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6875,7 +7072,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Noé prend le ballon rouge. Une goutte tombe, ploc. Le ballon roule. Noé dit : chien. Ouaf. Maman répète le cri. On dit le nom de l'animal. On dit le cri.</t>
+          <t>Noé prend le ballon rouge. Une goutte tombe, ploc. Le ballon roule. Chien. Ouaf. Maman répète le cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7013,6 +7210,12 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le ballon rouge. Une goutte tombe, ploc. Le ballon roule.
+enfant-m|Chien. Ouaf. Maman répète le cri. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7203,6 +7406,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7227,7 +7435,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. Le tissu est tout doux. On boit une gorgée. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range. Maman dit : c'est bien.</t>
+          <t>Noé rejoint Tom. Le tissu est tout doux. On boit une gorgée. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7365,6 +7573,12 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Le tissu est tout doux. On boit une gorgée. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7741,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7908,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Une cuillère tinte. On feuillette le livre. On a dit le nom de l'animal. On a dit le cri. Canard, coin coin. On dit le nom de l'animal. On dit le cri. On souffle. Noé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8075,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8242,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Le sable est tiède. On referme le livre. On a dit le nom de l'animal. On a dit le cri. Mouton, béé. On dit le nom de l'animal. On dit le cri. Noé prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8409,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8576,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le seau bleu. Le vent est doux sur la joue. Le seau est bleu. Dedans, une image de canard. Coin coin. Nom de l'animal, cri. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8769,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8938,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Un rire court, tout petit. On pose le ballon. On a dit le nom de l'animal. On a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9105,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9272,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Le papier froisse, chut. On secoue le sable. On a dit le nom de l'animal. On a dit le cri. Chat, miaou. On dit le nom de l'animal. On dit le cri. Maman serre Noé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9439,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9606,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. L'herbe chatouille le mollet. On caresse le tissu. On a dit le nom de l'animal. On a dit le cri. Vache, meuh. On dit le nom de l'animal. On dit le cri. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9773,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9940,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le doudou. Le lait est froid dans le verre. Le doudou sent le propre. Noé dit tout bas : vache, meuh. Le cri. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9851,6 +10135,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9875,7 +10164,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. Un pigeon roucoule. On tend la main. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range. Maman dit : c'est bien.</t>
+          <t>Noé rejoint Tom. Un pigeon roucoule. On tend la main. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10013,6 +10302,12 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Un pigeon roucoule. On tend la main. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10470,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10637,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. La fenêtre vibre un peu. On chante un petit air. On a dit le nom de l'animal. On a dit le cri. Canard, coin coin. On dit le nom de l'animal. On dit le cri. On souffle. Noé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10804,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10971,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Le lait est froid dans le verre. On compte jusqu'à trois. On a dit le nom de l'animal. On a dit le cri. Mouton, béé. On dit le nom de l'animal. On dit le cri. Noé prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11138,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11167,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers la chambre de repos. La couverture est douce. Un livre montre un canard. Maman dit : canard. Coin coin. Le nom de l'animal, c'est canard. Le cri, c'est coin coin. On dit le nom de l'animal. On dit le cri.</t>
+          <t>Noé va vers la chambre de repos. La couverture est douce. Un livre montre un canard. Canard. Coin coin. Le nom de l'animal, c'est canard. Le cri, c'est coin coin. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11305,13 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers la chambre de repos. La couverture est douce. Un livre montre un canard.
+maman|Canard. Coin coin.
+narrateur|Le nom de l'animal, c'est canard. Le cri, c'est coin coin. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11161,6 +11488,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|La vache fait meuh. On dit quoi ?</t>
         </is>
       </c>
     </row>
@@ -11329,6 +11661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Vache, meuh. Noé retient le cri. Maman est là. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11515,6 +11852,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11539,7 +11881,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Noé prend le ballon rouge. La corde du sac est rêche. Noé tape le ballon, tout doux. Maman dit : encore le cri. Ouaf. On dit le nom de l'animal. On dit le cri.</t>
+          <t>Noé prend le ballon rouge. La corde du sac est rêche. Noé tape le ballon, tout doux. Encore le cri. Ouaf. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11677,6 +12019,12 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le ballon rouge. La corde du sac est rêche. Noé tape le ballon, tout doux.
+maman|Encore le cri. Ouaf. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11865,6 +12213,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12029,6 +12382,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. La corde du sac est rêche. On montre du doigt. On a dit le nom de l'animal. On a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12191,6 +12549,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12353,6 +12716,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Le savon mousse entre les doigts. On range la chaise. On a dit le nom de l'animal. On a dit le cri. Chat, miaou. On dit le nom de l'animal. On dit le cri. Maman serre Noé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12515,6 +12883,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12677,6 +13050,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Un ruisseau chante. On range un objet. On a dit le nom de l'animal. On a dit le cri. Vache, meuh. On dit le nom de l'animal. On dit le cri. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12839,6 +13217,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13001,6 +13384,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le seau bleu. Ça sent le pain tiède. Noé pose le seau. Un oiseau chante. Ce n'est pas un cri de chien. On nomme. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13191,6 +13579,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13215,7 +13608,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint Tom. La laine gratte un peu. On se tient la main. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range. Maman dit : c'est bien.</t>
+          <t>Noé rejoint Tom. La laine gratte un peu. On se tient la main. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13353,6 +13746,12 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. La laine gratte un peu. On se tient la main. On a dit le nom de l'animal. On a dit le cri. Coq, cocorico. On dit le nom de l'animal. On dit le cri. Noé range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13515,6 +13914,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13677,6 +14081,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Un pain croustille. On dit merci. On a dit le nom de l'animal. On a dit le cri. Canard, coin coin. On dit le nom de l'animal. On dit le cri. On souffle. Noé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13839,6 +14248,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14001,6 +14415,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Le savon glisse. On souffle doucement. On a dit le nom de l'animal. On a dit le cri. Mouton, béé. On dit le nom de l'animal. On dit le cri. Noé prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14163,6 +14582,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14187,7 +14611,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Noé prend le doudou. Une plume vole. Noé câline le doudou. Maman dit : nom de l'animal, puis cri. Noé répète. On dit le nom de l'animal. On dit le cri.</t>
+          <t>Noé prend le doudou. Une plume vole. Noé câline le doudou. Nom de l'animal, puis cri. Noé répète. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14325,6 +14749,13 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le doudou. Une plume vole. Noé câline le doudou.
+maman|Nom de l'animal, puis cri.
+narrateur|Noé répète. On dit le nom de l'animal. On dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14513,6 +14944,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14677,6 +15113,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Une plume vole. On écoute jusqu'au bout. On a dit le nom de l'animal. On a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14839,6 +15280,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15001,6 +15447,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Le banc est lisse. On attend son tour. On a dit le nom de l'animal. On a dit le cri. Chat, miaou. On dit le nom de l'animal. On dit le cri. Maman serre Noé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15163,6 +15614,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15325,6 +15781,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Un grelot sonne. On sourit ensemble. On a dit le nom de l'animal. On a dit le cri. Vache, meuh. On dit le nom de l'animal. On dit le cri. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15487,6 +15948,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15505,7 +15971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15578,6 +16044,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-VIV-001.xlsx
+++ b/stories/arbres/TREE-VIV-001.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1326,6 +1331,11 @@
 enfant-m|Chat. Miaou. On nomme l'animal. On dit le cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1517,6 +1527,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1697,7 @@
 narrateur|Le cri, c'est meuh. Noé répète : vache. Meuh. Le nom de l'animal, et le cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1871,6 +1883,11 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>narrateur|Le chien fait ouaf. Quel est son cri ?</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2044,6 +2061,11 @@
           <t>narrateur|Oui. Noé a dit le nom de l'animal. Noé a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2257,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2404,6 +2427,7 @@
 narrateur|Noé dit le nom de l'animal. Noé dit le cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2599,6 +2623,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2766,6 +2791,11 @@
           <t>narrateur|Noé rejoint Tom. La lumière est claire. On parle tout bas. On a dit le nom de l'animal. On a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2933,6 +2963,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3100,6 +3131,7 @@
           <t>narrateur|Noé rejoint Léa. Des miettes dorment sur la table. On range les jouets. On a dit le nom de l'animal. On a dit le cri. Chat, miaou. On dit le nom de l'animal. On dit le cri. Maman serre Noé tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3267,6 +3299,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3434,6 +3467,7 @@
           <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On s'assoit un moment. On a dit le nom de l'animal. On a dit le cri. Vache, meuh. On dit le nom de l'animal. On dit le cri. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3601,6 +3635,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3768,6 +3803,7 @@
           <t>narrateur|Noé prend le seau bleu. Un pain croustille. Dans le seau, un dessin de coq. Cocorico. Noé nomme l'animal. Noé dit le cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3963,6 +3999,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4131,6 +4168,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4298,6 +4336,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4465,6 +4504,7 @@
           <t>narrateur|Noé rejoint Léa. La couverture est douce. On referme le sac. On a dit le nom de l'animal. On a dit le cri. Canard, coin coin. On dit le nom de l'animal. On dit le cri. On souffle. Noé sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4632,6 +4672,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4799,6 +4840,7 @@
           <t>narrateur|Noé rejoint Sami. Une cloche tinte au loin. On essuie une miette. On a dit le nom de l'animal. On a dit le cri. Mouton, béé. On dit le nom de l'animal. On dit le cri. Noé prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4966,6 +5008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5133,6 +5176,7 @@
           <t>narrateur|Noé prend le doudou. Un pain croustille. Noé serre le doudou. Le doudou a des oreilles de chat. Miaou. Nom de l'animal, cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5328,6 +5372,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5495,6 +5540,11 @@
           <t>narrateur|Noé rejoint Tom. Le bois sent le chaud. On met le doudou près. On a dit le nom de l'animal. On a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5662,6 +5712,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5829,6 +5880,7 @@
           <t>narrateur|Noé rejoint Léa. Une goutte tombe, ploc. On lace les chaussures. On a dit le nom de l'animal. On a dit le cri. Chat, miaou. On dit le nom de l'animal. On dit le cri. Maman serre Noé tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5996,6 +6048,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6163,6 +6216,7 @@
           <t>narrateur|Noé rejoint Sami. Le savon sent la fleur. On met le manteau. On a dit le nom de l'animal. On a dit le cri. Vache, meuh. On dit le nom de l'animal. On dit le cri. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6330,6 +6384,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6499,6 +6554,7 @@
 narrateur|Noé dit le nom de l'animal. Noé dit le cri. Cocorico. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6686,6 +6742,7 @@
           <t>narrateur|Miaou. C'est le cri de qui ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6857,6 +6914,7 @@
           <t>narrateur|Oui. Chat, miaou. Maman sourit. Nom de l'animal, cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7048,6 +7106,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7216,6 +7275,11 @@
 enfant-m|Chien. Ouaf. Maman répète le cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7411,6 +7475,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7579,6 +7644,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7746,6 +7812,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7913,6 +7980,7 @@
           <t>narrateur|Noé rejoint Léa. Une cuillère tinte. On feuillette le livre. On a dit le nom de l'animal. On a dit le cri. Canard, coin coin. On dit le nom de l'animal. On dit le cri. On souffle. Noé sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8080,6 +8148,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8247,6 +8316,7 @@
           <t>narrateur|Noé rejoint Sami. Le sable est tiède. On referme le livre. On a dit le nom de l'animal. On a dit le cri. Mouton, béé. On dit le nom de l'animal. On dit le cri. Noé prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8414,6 +8484,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8581,6 +8652,7 @@
           <t>narrateur|Noé prend le seau bleu. Le vent est doux sur la joue. Le seau est bleu. Dedans, une image de canard. Coin coin. Nom de l'animal, cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8776,6 +8848,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8943,6 +9016,11 @@
           <t>narrateur|Noé rejoint Tom. Un rire court, tout petit. On pose le ballon. On a dit le nom de l'animal. On a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9110,6 +9188,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9277,6 +9356,7 @@
           <t>narrateur|Noé rejoint Léa. Le papier froisse, chut. On secoue le sable. On a dit le nom de l'animal. On a dit le cri. Chat, miaou. On dit le nom de l'animal. On dit le cri. Maman serre Noé tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9444,6 +9524,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9611,6 +9692,7 @@
           <t>narrateur|Noé rejoint Sami. L'herbe chatouille le mollet. On caresse le tissu. On a dit le nom de l'animal. On a dit le cri. Vache, meuh. On dit le nom de l'animal. On dit le cri. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9778,6 +9860,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9945,6 +10028,7 @@
           <t>narrateur|Noé prend le doudou. Le lait est froid dans le verre. Le doudou sent le propre. Noé dit tout bas : vache, meuh. Le cri. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10140,6 +10224,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10308,6 +10393,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10475,6 +10561,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10642,6 +10729,7 @@
           <t>narrateur|Noé rejoint Léa. La fenêtre vibre un peu. On chante un petit air. On a dit le nom de l'animal. On a dit le cri. Canard, coin coin. On dit le nom de l'animal. On dit le cri. On souffle. Noé sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10809,6 +10897,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10976,6 +11065,7 @@
           <t>narrateur|Noé rejoint Sami. Le lait est froid dans le verre. On compte jusqu'à trois. On a dit le nom de l'animal. On a dit le cri. Mouton, béé. On dit le nom de l'animal. On dit le cri. Noé prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11143,6 +11233,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11312,6 +11403,7 @@
 narrateur|Le nom de l'animal, c'est canard. Le cri, c'est coin coin. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11495,6 +11587,7 @@
           <t>narrateur|La vache fait meuh. On dit quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11666,6 +11759,7 @@
           <t>narrateur|Oui. Vache, meuh. Noé retient le cri. Maman est là. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11857,6 +11951,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12025,6 +12120,7 @@
 maman|Encore le cri. Ouaf. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12220,6 +12316,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12387,6 +12484,11 @@
           <t>narrateur|Noé rejoint Tom. La corde du sac est rêche. On montre du doigt. On a dit le nom de l'animal. On a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12554,6 +12656,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12721,6 +12824,7 @@
           <t>narrateur|Noé rejoint Léa. Le savon mousse entre les doigts. On range la chaise. On a dit le nom de l'animal. On a dit le cri. Chat, miaou. On dit le nom de l'animal. On dit le cri. Maman serre Noé tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12888,6 +12992,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13055,6 +13160,7 @@
           <t>narrateur|Noé rejoint Sami. Un ruisseau chante. On range un objet. On a dit le nom de l'animal. On a dit le cri. Vache, meuh. On dit le nom de l'animal. On dit le cri. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13222,6 +13328,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13389,6 +13496,11 @@
           <t>narrateur|Noé prend le seau bleu. Ça sent le pain tiède. Noé pose le seau. Un oiseau chante. Ce n'est pas un cri de chien. On nomme. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13584,6 +13696,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13752,6 +13865,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13919,6 +14033,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14086,6 +14201,7 @@
           <t>narrateur|Noé rejoint Léa. Un pain croustille. On dit merci. On a dit le nom de l'animal. On a dit le cri. Canard, coin coin. On dit le nom de l'animal. On dit le cri. On souffle. Noé sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14253,6 +14369,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14420,6 +14537,7 @@
           <t>narrateur|Noé rejoint Sami. Le savon glisse. On souffle doucement. On a dit le nom de l'animal. On a dit le cri. Mouton, béé. On dit le nom de l'animal. On dit le cri. Noé prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14587,6 +14705,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14756,6 +14875,7 @@
 narrateur|Noé répète. On dit le nom de l'animal. On dit le cri.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14951,6 +15071,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15118,6 +15239,11 @@
           <t>narrateur|Noé rejoint Tom. Une plume vole. On écoute jusqu'au bout. On a dit le nom de l'animal. On a dit le cri. Chien, ouaf. On dit le nom de l'animal. On dit le cri. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15285,6 +15411,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15452,6 +15579,7 @@
           <t>narrateur|Noé rejoint Léa. Le banc est lisse. On attend son tour. On a dit le nom de l'animal. On a dit le cri. Chat, miaou. On dit le nom de l'animal. On dit le cri. Maman serre Noé tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15619,6 +15747,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15786,6 +15915,7 @@
           <t>narrateur|Noé rejoint Sami. Un grelot sonne. On sourit ensemble. On a dit le nom de l'animal. On a dit le cri. Vache, meuh. On dit le nom de l'animal. On dit le cri. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15953,6 +16083,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15971,7 +16102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16051,6 +16182,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16065,7 +16210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16252,6 +16397,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
